--- a/data/age_indexes/excel_files/a1_min_age_indexes.xlsx
+++ b/data/age_indexes/excel_files/a1_min_age_indexes.xlsx
@@ -7,12 +7,13 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="run1" sheetId="1" r:id="rId1"/>
-    <sheet name="run2" sheetId="2" r:id="rId2"/>
-    <sheet name="run3" sheetId="3" r:id="rId3"/>
-    <sheet name="run4" sheetId="4" r:id="rId4"/>
-    <sheet name="run5" sheetId="5" r:id="rId5"/>
-    <sheet name="best" sheetId="6" r:id="rId6"/>
+    <sheet name="run0" sheetId="1" r:id="rId1"/>
+    <sheet name="run1" sheetId="2" r:id="rId2"/>
+    <sheet name="run2" sheetId="3" r:id="rId3"/>
+    <sheet name="run3" sheetId="4" r:id="rId4"/>
+    <sheet name="run4" sheetId="5" r:id="rId5"/>
+    <sheet name="run5" sheetId="6" r:id="rId6"/>
+    <sheet name="best" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -367,7 +368,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -384,7 +385,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ELF2, FOXA3</t>
         </is>
       </c>
     </row>
@@ -396,7 +402,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOX2, NFATC2</t>
         </is>
       </c>
     </row>
@@ -408,7 +419,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EGF, E2F8</t>
         </is>
       </c>
     </row>
@@ -420,7 +436,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SPI1, E2F8</t>
         </is>
       </c>
     </row>
@@ -432,7 +453,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GZF1, HOXA7</t>
         </is>
       </c>
     </row>
@@ -444,7 +470,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FOXF1</t>
         </is>
       </c>
     </row>
@@ -456,7 +487,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MYB, APC</t>
         </is>
       </c>
     </row>
@@ -468,7 +504,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PAX5, GATA1, HIPK2</t>
         </is>
       </c>
     </row>
@@ -480,7 +521,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MYF6, NKX2-3, OTX1, EN1</t>
         </is>
       </c>
     </row>
@@ -492,7 +538,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HOXD3, CTCFL, CDX1</t>
         </is>
       </c>
     </row>
@@ -504,7 +555,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GATA1</t>
         </is>
       </c>
     </row>
@@ -516,7 +572,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FOXA1, NR1H4, ETV4</t>
         </is>
       </c>
     </row>
@@ -528,7 +589,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IRF8, HEYL, HOXA1</t>
         </is>
       </c>
     </row>
@@ -540,7 +606,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HOPX, FHL2, NKX2-5</t>
         </is>
       </c>
     </row>
@@ -552,7 +623,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GATA4, NANOG, TP63</t>
         </is>
       </c>
     </row>
@@ -564,7 +640,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HEYL, CDX2</t>
         </is>
       </c>
     </row>
@@ -576,7 +657,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NANOG, CDX2</t>
         </is>
       </c>
     </row>
@@ -588,7 +674,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>POU4F1, CRABP2</t>
         </is>
       </c>
     </row>
@@ -600,7 +691,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MYB, BMI1</t>
         </is>
       </c>
     </row>
@@ -612,7 +708,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IRF8, DLX4</t>
         </is>
       </c>
     </row>
@@ -624,7 +725,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEDD, NR4A2, HEY1, HR</t>
         </is>
       </c>
     </row>
@@ -636,7 +742,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EBF3, GTF2F1, CRABP2</t>
         </is>
       </c>
     </row>
@@ -648,7 +759,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BATF</t>
         </is>
       </c>
     </row>
@@ -660,7 +776,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IRF6</t>
         </is>
       </c>
     </row>
@@ -672,7 +793,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FOXA1, HOXA7</t>
         </is>
       </c>
     </row>
@@ -684,7 +810,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FOXP3, KLF11</t>
         </is>
       </c>
     </row>
@@ -696,7 +827,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FOXG1, BATF</t>
         </is>
       </c>
     </row>
@@ -708,7 +844,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TLX1, GLI1, BRIP1</t>
         </is>
       </c>
     </row>
@@ -720,7 +861,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LIMD1, PAX8</t>
         </is>
       </c>
     </row>
@@ -732,7 +878,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TP53BP1, E2F8</t>
         </is>
       </c>
     </row>
@@ -744,7 +895,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ARID3A</t>
         </is>
       </c>
     </row>
@@ -756,7 +912,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HTATIP2, AES</t>
         </is>
       </c>
     </row>
@@ -768,7 +929,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BATF, ETV5, EHF, HES6</t>
         </is>
       </c>
     </row>
@@ -780,7 +946,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BATF, FOXA3</t>
         </is>
       </c>
     </row>
@@ -792,7 +963,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HEY1, CEBPA, ETV5</t>
         </is>
       </c>
     </row>
@@ -804,7 +980,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NR0B1, CRX</t>
         </is>
       </c>
     </row>
@@ -816,7 +997,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FOSB, ELF2</t>
         </is>
       </c>
     </row>
@@ -828,7 +1014,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FOXD3, GATA2, ARID3A, KDM4B</t>
         </is>
       </c>
     </row>
@@ -840,7 +1031,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CEBPE, EGR2</t>
         </is>
       </c>
     </row>
@@ -852,7 +1048,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>KLF15, AES</t>
         </is>
       </c>
     </row>
@@ -864,7 +1065,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SNIP1, AES</t>
         </is>
       </c>
     </row>
@@ -876,7 +1082,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ARID3A, CEBPE, FOXL2</t>
         </is>
       </c>
     </row>
@@ -888,7 +1099,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EZH2, ETS2</t>
         </is>
       </c>
     </row>
@@ -900,7 +1116,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CEBPZ, ID3</t>
         </is>
       </c>
     </row>
@@ -912,7 +1133,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BATF, FOXL2, TRIM16</t>
         </is>
       </c>
     </row>
@@ -924,7 +1150,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FHL2, CEBPE</t>
         </is>
       </c>
     </row>
@@ -936,7 +1167,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ETV4, BIN1</t>
         </is>
       </c>
     </row>
@@ -948,7 +1184,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AHR, ATF6</t>
         </is>
       </c>
     </row>
@@ -970,7 +1211,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1573,7 +1814,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2176,7 +2417,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2779,7 +3020,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -3382,7 +3623,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -3964,6 +4205,849 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tissue</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Gene_Set</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adipose_subcutaneous</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ELF2, FOXA3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adipose_visceral_omentum</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOX2, NFATC2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adrenal_gland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EGF, E2F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>artery_aorta</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SPI1, E2F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>artery_coronary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GZF1, HOXA7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>artery_tibial</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FOXF1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>brain_amygdala</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MYB, APC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>brain_anterior_cingulate_cortex_ba24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PAX5, GATA1, HIPK2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>brain_caudate_basal_ganglia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MYF6, NKX2-3, OTX1, EN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>brain_cerebellar_hemisphere</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HOXD3, CTCFL, CDX1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>brain_cerebellum</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GATA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>brain_cortex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FOXA1, NR1H4, ETV4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>brain_frontal_cortex_ba9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IRF8, HEYL, HOXA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>brain_hippocampus</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HOPX, FHL2, NKX2-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>brain_hypothalamus</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GATA4, NANOG, TP63</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>brain_nucleus_accumbens_basal ganglia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HEYL, CDX2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>brain_putamen_basal_ganglia</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NANOG, CDX2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>brain_spinal_cord_cervical_c-1)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>POU4F1, CRABP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>brain_substantia_nigra</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MYB, BMI1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>breast_mammary_tissue</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IRF8, DLX4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cells_cultured_fibroblasts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEDD, NR4A2, HEY1, HR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cells_ebv-transformed_lymphocytes</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EBF3, GTF2F1, CRABP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>colon_sigmoid</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BATF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>colon_transverse</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IRF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>esophagus_gastroesophageal_junction</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FOXA1, HOXA7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>esophagus_mucosa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FOXP3, KLF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>esophagus_muscularis</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FOXG1, BATF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>heart_atrial_appendage</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TLX1, GLI1, BRIP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>heart_left_ventricle</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LIMD1, PAX8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>liver</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TP53BP1, E2F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>lung</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ARID3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>minor_salivary_gland</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HTATIP2, AES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>muscle_skeletal</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BATF, ETV5, EHF, HES6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>nerve_tibial</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BATF, FOXA3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ovary</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HEY1, CEBPA, ETV5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>pancreas</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>-0.466666666666667</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NR0B1, CRX</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>pituitary</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FOSB, ELF2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>prostate</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FOXD3, GATA2, ARID3A, KDM4B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>skin_not_sun_exposed_suprapubic</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CEBPE, EGR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>skin_sun_exposed_lower_leg</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>KLF15, AES</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>small_intestine_terminal_ileum</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-0.533333333333333</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SNIP1, AES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>spleen</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ARID3A, CEBPE, FOXL2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>stomach</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EZH2, ETS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>testis</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CEBPZ, ID3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>thyroid</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BATF, FOXL2, TRIM16</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>uterus</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FHL2, CEBPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>vagina</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ETV4, BIN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>whole_blood</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AHR, ATF6</t>
         </is>
       </c>
     </row>
